--- a/data/seed_template.xlsx
+++ b/data/seed_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\tenopa proposer\-agent-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0F7C12-4796-45B1-AD3D-95AE3A2C80A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADC1886-072A-4148-87DC-B852C67E559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_조직" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
     <sheet name="4_사용자" sheetId="4" r:id="rId4"/>
     <sheet name="5_역량" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="147">
   <si>
     <t>조직명</t>
   </si>
@@ -44,9 +57,6 @@
     <t>소속 조직명</t>
   </si>
   <si>
-    <t>디지털사업본부</t>
-  </si>
-  <si>
     <t>팀명</t>
   </si>
   <si>
@@ -59,9 +69,6 @@
     <t>선택</t>
   </si>
   <si>
-    <t>https://outlook.office.com/webhook/...</t>
-  </si>
-  <si>
     <t>이메일</t>
   </si>
   <si>
@@ -144,10 +151,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>전략기술본부</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>기술사업화본부</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -172,22 +175,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>AX전략1팀</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전략1팀</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전략2팀</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전략3팀</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>혁신전략본부</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -196,10 +183,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>김수연</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>김상준</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -244,10 +227,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>부사장</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>파트너</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -304,42 +283,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>신근호</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>김종석</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이윤유</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>김정현</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>심우진</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>나병민</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상범</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>조기정</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>오서현</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>김연정</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -416,10 +359,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>sykim@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>sjk@tenopa.co.kr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -500,42 +439,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>geunho123@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>jskim@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ywlee@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>hyun768@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim5892@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>byungmina@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>tkd8420@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>chokj0416@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>shoh@tenopa.co.kr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>redhood@tenopa.co.kr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -620,15 +523,75 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>AX연구소</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>leedj@tenopa.co.kr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>AX혁신팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술사업화1팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>특화 분야</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>필수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재안안전, 원자력, 토양지하수, 환경보험, 유해물질, 재생의료, 양자, 자율제조, 지역혁신</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI업무자동화, AI 교육훈련, AX컨설팅</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>스케일업팁스, 기술사업화, 벤처성장지원, 딥테크챌린지, PMO(프로젝트관리)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI시티, AI빅데이터, 피지컬먀, 정신건강, 필수의료, 예타기획</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>혁신3팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강관리, 재생의료, 정신건강, 의료기기, 마약류안전관리, 고령친화, 만성질환관리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>성과분석, 정밀의료, 동향조사, 감염병, 바이오빅데이터, 바이오헬스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>과학기술인재, 신산업정책, AI안전, 탄소소재, 국토교통, 탄소중립, 기후변화대응</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AX1팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>T2B1팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>AX추진팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전민경</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>jmk@tenopa.co.kr</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -690,7 +653,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -718,6 +681,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +719,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -767,7 +736,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1089,7 +1059,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
@@ -1105,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1130,15 +1100,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -1146,7 +1116,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -1154,7 +1124,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -1162,17 +1132,9 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1184,95 +1146,125 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="3" max="3" width="40.5" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="C9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1282,40 +1274,41 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="25.59765625" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="7" width="20" customWidth="1"/>
+    <col min="5" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="11.3984375" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
@@ -1330,36 +1323,36 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
@@ -1368,22 +1361,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="6" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
@@ -1392,22 +1385,22 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>2</v>
@@ -1415,47 +1408,47 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="A6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="7" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>2</v>
@@ -1463,47 +1456,47 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>2</v>
@@ -1512,22 +1505,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>2</v>
@@ -1536,22 +1529,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>2</v>
@@ -1560,22 +1553,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>2</v>
@@ -1584,22 +1577,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>2</v>
@@ -1608,22 +1601,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>2</v>
@@ -1632,70 +1625,70 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="A16" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="11" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="7" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>2</v>
@@ -1704,22 +1697,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="7" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>2</v>
@@ -1728,22 +1721,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>2</v>
@@ -1752,22 +1745,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>2</v>
@@ -1776,22 +1769,22 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="7" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>2</v>
@@ -1800,22 +1793,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="6" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>2</v>
@@ -1824,22 +1817,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>2</v>
@@ -1848,22 +1841,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>2</v>
@@ -1872,22 +1865,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>2</v>
@@ -1896,22 +1889,22 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="E26" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>2</v>
@@ -1920,22 +1913,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>2</v>
@@ -1944,22 +1937,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G28" s="8" t="s">
         <v>2</v>
@@ -1968,22 +1961,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>2</v>
@@ -1992,190 +1985,190 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="8" t="s">
+      <c r="C33" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A32" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A33" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G34" s="8" t="s">
+      <c r="D34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A35" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="8" t="s">
+      <c r="A35" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="D35" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="8" t="s">
+      <c r="A36" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G36" s="8" t="s">
+      <c r="D36" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="6" t="s">
-        <v>133</v>
+      <c r="A37" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="D37" s="3" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>2</v>
@@ -2183,297 +2176,72 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="6" t="s">
-        <v>134</v>
+      <c r="A38" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A41" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G41" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A43" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A45" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A46" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A47" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H47" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorTitle="잘못된 역할" error="member, lead, director, executive, admin 중 선택하세요." sqref="D48:D201 D3:D47" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" errorTitle="잘못된 역할" error="member, lead, director, executive, admin 중 선택하세요." sqref="D3:D192" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"member,lead,director,executive,admin"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{9A6EBADA-21F5-42B8-96D6-634C3800B59D}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{4F1D5A45-E584-4F1F-BCC2-A35DD955B6E2}"/>
-    <hyperlink ref="A5" r:id="rId3" xr:uid="{292A2F38-D69E-489D-9C88-BE71D2BA707F}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{E8FF8B24-1BAC-45BE-94FC-9DAFD479245C}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{F565FC5D-6EE7-4353-8784-6461744E180C}"/>
-    <hyperlink ref="A8" r:id="rId6" xr:uid="{5DB50148-D62F-4AB5-9E33-C6FF82446625}"/>
-    <hyperlink ref="A11" r:id="rId7" xr:uid="{C9B41535-8AE6-4FA6-B1EB-797899015E0F}"/>
-    <hyperlink ref="A12" r:id="rId8" xr:uid="{E60C50CC-BA56-4ED4-8267-1E5D5E4A716C}"/>
-    <hyperlink ref="A13" r:id="rId9" xr:uid="{34ECED78-7637-447C-9B5E-D5FB7EE12EC6}"/>
-    <hyperlink ref="A14" r:id="rId10" xr:uid="{6F65C446-486C-4948-891E-49C101A8809A}"/>
-    <hyperlink ref="A15" r:id="rId11" xr:uid="{8D6C44A1-85A2-4CAA-8555-A0E381F6BA21}"/>
-    <hyperlink ref="A16" r:id="rId12" xr:uid="{56CC7D33-0D7B-4ADC-8947-B2CFD3D46E48}"/>
-    <hyperlink ref="A22" r:id="rId13" xr:uid="{03462123-4721-4F71-A222-DD1661CF1AC4}"/>
-    <hyperlink ref="A23" r:id="rId14" xr:uid="{F32A9395-363F-4672-A762-B21B9C64DEFF}"/>
-    <hyperlink ref="A24" r:id="rId15" xr:uid="{EDA6EC99-437F-4AB2-BC42-E7B8D424E772}"/>
-    <hyperlink ref="A25" r:id="rId16" xr:uid="{D51E54E0-080A-4D1F-8F93-4DE2650A88C6}"/>
-    <hyperlink ref="A26" r:id="rId17" xr:uid="{037E655A-95D9-42FC-9427-AA9E69530910}"/>
-    <hyperlink ref="A27" r:id="rId18" xr:uid="{FB75C4C3-0794-4CE6-9B8E-A04326003CAC}"/>
-    <hyperlink ref="A28" r:id="rId19" xr:uid="{121EE60F-E1EC-4A83-99FA-C8651F6D04FA}"/>
-    <hyperlink ref="A29" r:id="rId20" xr:uid="{9A406167-144D-475F-86F3-8C664A6424EE}"/>
-    <hyperlink ref="A30" r:id="rId21" xr:uid="{E16B32FA-60E8-48D6-A186-BDFEFFF568E7}"/>
-    <hyperlink ref="A31" r:id="rId22" xr:uid="{B8090F53-F572-4269-99A2-72DF29928ED6}"/>
-    <hyperlink ref="A32" r:id="rId23" xr:uid="{FB160C55-C004-4A54-A8A0-9D23240FFD7C}"/>
-    <hyperlink ref="A33" r:id="rId24" xr:uid="{D4455B89-90B9-42C5-842D-78A0C46FFE58}"/>
-    <hyperlink ref="A34" r:id="rId25" xr:uid="{03482D30-BBA7-42FD-82CE-0BE693F326EE}"/>
-    <hyperlink ref="A35" r:id="rId26" xr:uid="{F822060C-A7A5-4B3B-8B38-F89FB3F13095}"/>
-    <hyperlink ref="A36" r:id="rId27" xr:uid="{F31D51AD-D78C-4434-B076-35EFBB4FE85E}"/>
-    <hyperlink ref="A37" r:id="rId28" xr:uid="{BC5F5508-E10C-443F-B693-8348154085CB}"/>
-    <hyperlink ref="A38" r:id="rId29" xr:uid="{962CC806-19B9-4297-A5A6-72BBFF908A86}"/>
-    <hyperlink ref="A39" r:id="rId30" xr:uid="{56D7B1AF-C078-4D0C-B34D-C845B117BEDB}"/>
-    <hyperlink ref="A43" r:id="rId31" xr:uid="{8358B6BC-422D-488D-89BE-9FF460A46200}"/>
-    <hyperlink ref="A44" r:id="rId32" xr:uid="{C07BFD7F-A213-4340-A963-5A154D9D84B7}"/>
-    <hyperlink ref="A45" r:id="rId33" xr:uid="{BD85F4E9-A0E1-460F-8666-9BD25771B4F9}"/>
-    <hyperlink ref="A46" r:id="rId34" xr:uid="{8F284806-93E5-4290-BFB3-D2464EE79A23}"/>
-    <hyperlink ref="A47" r:id="rId35" xr:uid="{A9052831-1FCE-4650-8864-A6D385692170}"/>
-    <hyperlink ref="A9" r:id="rId36" xr:uid="{4CD8F5F7-A061-4BF9-A05B-49519C32CFC6}"/>
-    <hyperlink ref="A10" r:id="rId37" xr:uid="{A771047A-860C-425E-AE25-99239C864A10}"/>
-    <hyperlink ref="A17" r:id="rId38" xr:uid="{73661A9C-737D-4D60-8FB7-B83B1D3B9AB1}"/>
-    <hyperlink ref="A18" r:id="rId39" xr:uid="{C9F1C707-97CB-410F-99EC-5DCE5C4C6F77}"/>
-    <hyperlink ref="A19" r:id="rId40" xr:uid="{3FB019D2-6550-4C46-890B-19A6AC80DD6C}"/>
-    <hyperlink ref="A20" r:id="rId41" xr:uid="{1FEA6C7D-3229-4275-B2DF-E555C5D9139F}"/>
-    <hyperlink ref="A21" r:id="rId42" xr:uid="{8CF50D70-6CAE-4BF7-8216-9F9D5262D75E}"/>
-    <hyperlink ref="A40" r:id="rId43" xr:uid="{0486F9B2-1964-41FF-B5D6-A794A04AB634}"/>
-    <hyperlink ref="A41" r:id="rId44" xr:uid="{03ADBACE-C29F-4A4B-B51F-F2A64D6ECC1B}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{292A2F38-D69E-489D-9C88-BE71D2BA707F}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{E8FF8B24-1BAC-45BE-94FC-9DAFD479245C}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{F565FC5D-6EE7-4353-8784-6461744E180C}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{5DB50148-D62F-4AB5-9E33-C6FF82446625}"/>
+    <hyperlink ref="A10" r:id="rId6" xr:uid="{C9B41535-8AE6-4FA6-B1EB-797899015E0F}"/>
+    <hyperlink ref="A11" r:id="rId7" xr:uid="{E60C50CC-BA56-4ED4-8267-1E5D5E4A716C}"/>
+    <hyperlink ref="A12" r:id="rId8" xr:uid="{34ECED78-7637-447C-9B5E-D5FB7EE12EC6}"/>
+    <hyperlink ref="A13" r:id="rId9" xr:uid="{6F65C446-486C-4948-891E-49C101A8809A}"/>
+    <hyperlink ref="A14" r:id="rId10" xr:uid="{8D6C44A1-85A2-4CAA-8555-A0E381F6BA21}"/>
+    <hyperlink ref="A15" r:id="rId11" xr:uid="{56CC7D33-0D7B-4ADC-8947-B2CFD3D46E48}"/>
+    <hyperlink ref="A22" r:id="rId12" xr:uid="{03462123-4721-4F71-A222-DD1661CF1AC4}"/>
+    <hyperlink ref="A23" r:id="rId13" xr:uid="{F32A9395-363F-4672-A762-B21B9C64DEFF}"/>
+    <hyperlink ref="A24" r:id="rId14" xr:uid="{EDA6EC99-437F-4AB2-BC42-E7B8D424E772}"/>
+    <hyperlink ref="A25" r:id="rId15" xr:uid="{D51E54E0-080A-4D1F-8F93-4DE2650A88C6}"/>
+    <hyperlink ref="A26" r:id="rId16" xr:uid="{037E655A-95D9-42FC-9427-AA9E69530910}"/>
+    <hyperlink ref="A27" r:id="rId17" xr:uid="{FB75C4C3-0794-4CE6-9B8E-A04326003CAC}"/>
+    <hyperlink ref="A28" r:id="rId18" xr:uid="{121EE60F-E1EC-4A83-99FA-C8651F6D04FA}"/>
+    <hyperlink ref="A29" r:id="rId19" xr:uid="{9A406167-144D-475F-86F3-8C664A6424EE}"/>
+    <hyperlink ref="A30" r:id="rId20" xr:uid="{E16B32FA-60E8-48D6-A186-BDFEFFF568E7}"/>
+    <hyperlink ref="A34" r:id="rId21" xr:uid="{8358B6BC-422D-488D-89BE-9FF460A46200}"/>
+    <hyperlink ref="A35" r:id="rId22" xr:uid="{C07BFD7F-A213-4340-A963-5A154D9D84B7}"/>
+    <hyperlink ref="A36" r:id="rId23" xr:uid="{BD85F4E9-A0E1-460F-8666-9BD25771B4F9}"/>
+    <hyperlink ref="A37" r:id="rId24" xr:uid="{8F284806-93E5-4290-BFB3-D2464EE79A23}"/>
+    <hyperlink ref="A38" r:id="rId25" xr:uid="{A9052831-1FCE-4650-8864-A6D385692170}"/>
+    <hyperlink ref="A8" r:id="rId26" xr:uid="{4CD8F5F7-A061-4BF9-A05B-49519C32CFC6}"/>
+    <hyperlink ref="A9" r:id="rId27" xr:uid="{A771047A-860C-425E-AE25-99239C864A10}"/>
+    <hyperlink ref="A17" r:id="rId28" xr:uid="{73661A9C-737D-4D60-8FB7-B83B1D3B9AB1}"/>
+    <hyperlink ref="A18" r:id="rId29" xr:uid="{C9F1C707-97CB-410F-99EC-5DCE5C4C6F77}"/>
+    <hyperlink ref="A19" r:id="rId30" xr:uid="{3FB019D2-6550-4C46-890B-19A6AC80DD6C}"/>
+    <hyperlink ref="A20" r:id="rId31" xr:uid="{1FEA6C7D-3229-4275-B2DF-E555C5D9139F}"/>
+    <hyperlink ref="A21" r:id="rId32" xr:uid="{8CF50D70-6CAE-4BF7-8216-9F9D5262D75E}"/>
+    <hyperlink ref="A31" r:id="rId33" xr:uid="{0486F9B2-1964-41FF-B5D6-A794A04AB634}"/>
+    <hyperlink ref="A32" r:id="rId34" xr:uid="{03ADBACE-C29F-4A4B-B51F-F2A64D6ECC1B}"/>
+    <hyperlink ref="A16" r:id="rId35" xr:uid="{E0CE94F1-087B-4DDB-A713-1DB510A92863}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2493,16 +2261,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
@@ -2519,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>1</v>
@@ -2527,16 +2295,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>2</v>
@@ -2544,16 +2312,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>2</v>
@@ -2561,16 +2329,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>2</v>
@@ -2578,7 +2346,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
